--- a/02_Контуры_резки/Ведомость_заготовок.xlsx
+++ b/02_Контуры_резки/Ведомость_заготовок.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 455×60×2,9, L=1550</t>
+          <t>Деталь 1550×455×60</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -561,12 +561,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>455×60, L=1550</t>
+          <t>1550×455×60</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
@@ -577,7 +577,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Профиль резиновый 1200×346,4, L=6276,8</t>
+          <t>Полотно гибкое (резина), s=5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1200×346,4, L=6276,8</t>
+          <t>6528×2387, s=5</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
@@ -659,7 +659,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Раскрой по DXF (PSH24-000.01__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Деталь 250,5×244×130,5</t>
+          <t>Панель гнутая, s=4,7</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Заготовка (уточнить)</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>250,5×244×130,5</t>
+          <t>261×225, s=4,7</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -700,7 +700,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
+          <t>Раскрой по DXF (PSH24-000.02__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Деталь 250,5×230,2×139</t>
+          <t>Панель гнутая, s=4,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Заготовка (уточнить)</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>250,5×230,2×139</t>
+          <t>261×225, s=4,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
+          <t>Раскрой по DXF (PSH24-000.02-01-Variant2__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Профиль резиновый 171×32,8, L=5700</t>
+          <t>Полотно гибкое (резина), s=4,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>171×32,8, L=5700</t>
+          <t>5928×175, s=4,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
@@ -823,7 +823,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Раскрой по DXF (PSH24-000.04__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Стержень ⌀63, L=1026</t>
+          <t>Деталь 1026×63×63</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Пруток</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Ø63, L=1026</t>
+          <t>1026×63×63</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
@@ -864,7 +864,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер; дальнейшая обработка по чертежу</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Труба ⌀108×13,1, L=1338</t>
+          <t>Деталь 1338×108×108</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108×108, L=1338</t>
+          <t>1338×108×108</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
@@ -905,7 +905,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Профиль сплошной 105×15, L=1260</t>
+          <t>Деталь 1260×105×15</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>105×15, L=1260</t>
+          <t>1260×105×15</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
@@ -946,7 +946,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 168,7×62×2, L=5720</t>
+          <t>Панель гнутая, s=4,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168,7×62, L=5720</t>
+          <t>5949×181, s=4,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Раскрой по DXF (PSH24-001.01__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 168,7×62×2, L=5720</t>
+          <t>Панель гнутая, s=4,8</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>168,7×62, L=5720</t>
+          <t>5949×181, s=4,8</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Раскрой по DXF (PSH24-001.01-01__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 451×105×3,3, L=3500</t>
+          <t>Деталь 3500×451×105</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>451×105, L=3500</t>
+          <t>3500×451×105</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 451×105×3,3, L=3500</t>
+          <t>Деталь 3500×451×105</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>451×105, L=3500</t>
+          <t>3500×451×105</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 451×105×3,5, L=2105</t>
+          <t>Деталь 2105×451×105</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>451×105, L=2105</t>
+          <t>2105×451×105</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 451×105×3,5, L=2105</t>
+          <t>Деталь 2105×451×105</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1750,12 +1750,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>451×105, L=2105</t>
+          <t>2105×451×105</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Деталь 1561,4×1250×138,1</t>
+          <t>Панель гнутая, s=5</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Заготовка (уточнить)</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1561,4×1250×138,1</t>
+          <t>1624×1324, s=5</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
+          <t>Раскрой по DXF (PSH24-021.01__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 250×138,1×1,8, L=1561,4</t>
+          <t>Панель гнутая, s=4,9</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>250×138,1, L=1561,4</t>
+          <t>1624×269, s=4,9</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Раскрой по DXF (PSH24-021.06__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Труба ⌀30×2, L=894</t>
+          <t>Деталь 894×30×30</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>30×30, L=894</t>
+          <t>894×30×30</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 600×85×2,8, L=3004</t>
+          <t>Деталь 3004×600×85</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>600×85, L=3004</t>
+          <t>3004×600×85</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 600×85×2,8, L=3004</t>
+          <t>Деталь 3004×600×85</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>600×85, L=3004</t>
+          <t>3004×600×85</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 600×85×2,9, L=2500</t>
+          <t>Деталь 2500×600×85</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>600×85, L=2500</t>
+          <t>2500×600×85</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Деталь 1561,4×1000×138,1</t>
+          <t>Панель гнутая, s=5</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3144,12 +3144,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Заготовка (уточнить)</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>1561,4×1000×138,1</t>
+          <t>1624×1061, s=5</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
+          <t>Раскрой по DXF (PSH24-026.01__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Деталь 1561,4×1000×138,1</t>
+          <t>Панель гнутая, s=5</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Заготовка (уточнить)</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>1561,4×1000×138,1</t>
+          <t>1624×1061, s=5</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
+          <t>Раскрой по DXF (PSH24-026.01-01__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 80×45×4,9, L=2128</t>
+          <t>Деталь 2128×80×45</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>80×45, L=2128</t>
+          <t>2128×80×45</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Труба ⌀50×3,3, L=1410</t>
+          <t>Деталь 1410×50×50</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>50×50, L=1410</t>
+          <t>1410×50×50</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Труба ⌀50×3,3, L=1207</t>
+          <t>Деталь 1207×50×50</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3349,12 +3349,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>50×50, L=1207</t>
+          <t>1207×50×50</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Деталь 80×80×60,6</t>
+          <t>Панель гнутая, s=3,6</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Заготовка (уточнить)</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>80×80×60,6</t>
+          <t>83×159, s=3,6</t>
         </is>
       </c>
       <c r="G81" s="2" t="n">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
+          <t>Раскрой по DXF (PSH24-034.02__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Деталь 126,5×80×80</t>
+          <t>Панель гнутая, s=3,9</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Заготовка (уточнить)</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>126,5×80×80</t>
+          <t>132×276, s=3,9</t>
         </is>
       </c>
       <c r="G82" s="2" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
+          <t>Раскрой по DXF (PSH24-034.03__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Деталь 223,4×80×80</t>
+          <t>Панель гнутая, s=3,9</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Заготовка (уточнить)</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>223,4×80×80</t>
+          <t>232×279, s=3,9</t>
         </is>
       </c>
       <c r="G83" s="2" t="n">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
+          <t>Раскрой по DXF (PSH24-034.04__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Стержень ⌀20, L=150</t>
+          <t>Деталь 150×20×20</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Пруток</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Ø20, L=150</t>
+          <t>150×20×20</t>
         </is>
       </c>
       <c r="G90" s="2" t="n">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер; дальнейшая обработка по чертежу</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Труба ⌀480,9×1,3, L=1510</t>
+          <t>Панель гнутая, s=2</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>480,9×463, L=1510</t>
+          <t>157×932, s=2</t>
         </is>
       </c>
       <c r="G91" s="2" t="n">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Раскрой по DXF (PSH24-041.01__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 120×55×2,4, L=1510</t>
+          <t>Деталь 1510×120×55</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>120×55, L=1510</t>
+          <t>1510×120×55</t>
         </is>
       </c>
       <c r="G93" s="2" t="n">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Стержень ⌀95, L=2052</t>
+          <t>Деталь 2052×95×95</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Пруток</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Ø95, L=2052</t>
+          <t>2052×95×95</t>
         </is>
       </c>
       <c r="G96" s="2" t="n">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер; дальнейшая обработка по чертежу</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Стержень ⌀75, L=1660</t>
+          <t>Деталь 1660×75×75</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Пруток</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Ø75, L=1660</t>
+          <t>1660×75×75</t>
         </is>
       </c>
       <c r="G99" s="2" t="n">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер; дальнейшая обработка по чертежу</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Профиль сплошной 100×20, L=326</t>
+          <t>Деталь 326×100×20</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>100×20, L=326</t>
+          <t>326×100×20</t>
         </is>
       </c>
       <c r="G100" s="2" t="n">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Деталь 336×192×140</t>
+          <t>Панель гнутая, s=2</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Заготовка (уточнить)</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>336×192×140</t>
+          <t>349×233, s=2</t>
         </is>
       </c>
       <c r="G101" s="2" t="n">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
+          <t>Раскрой по DXF (PSH24-044.02__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Деталь 340×192×140</t>
+          <t>Панель гнутая, s=1,9</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Заготовка (уточнить)</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>340×192×140</t>
+          <t>354×231, s=1,9</t>
         </is>
       </c>
       <c r="G102" s="2" t="n">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
+          <t>Раскрой по DXF (PSH24-044.03__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Стержень ⌀36, L=500</t>
+          <t>Деталь 500×36×36</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Пруток</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Ø36, L=500</t>
+          <t>500×36×36</t>
         </is>
       </c>
       <c r="G105" s="2" t="n">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер; дальнейшая обработка по чертежу</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Деталь 1550×1027,1×95,1</t>
+          <t>Панель гнутая, s=3</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Заготовка (уточнить)</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>1550×1027,1×95,1</t>
+          <t>1612×1021, s=3</t>
         </is>
       </c>
       <c r="G106" s="2" t="n">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
+          <t>Раскрой по DXF (PSH24-050.01__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 80×60×3,8, L=1320</t>
+          <t>Деталь 1320×80×60</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>80×60, L=1320</t>
+          <t>1320×80×60</t>
         </is>
       </c>
       <c r="G108" s="2" t="n">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Деталь 946×696×30</t>
+          <t>Панель гнутая, s=3</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Заготовка (уточнить)</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>946×696×30</t>
+          <t>984×753, s=3</t>
         </is>
       </c>
       <c r="G109" s="2" t="n">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
+          <t>Раскрой по DXF (PSH24-050.06__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Деталь 764×455×105</t>
+          <t>Панель гнутая, s=5,9</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Заготовка (уточнить)</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>764×455×105</t>
+          <t>795×695, s=5,9</t>
         </is>
       </c>
       <c r="G110" s="2" t="n">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
+          <t>Раскрой по DXF (PSH24-052.01__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Деталь 764×455×105</t>
+          <t>Панель гнутая, s=5,9</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Заготовка (уточнить)</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>764×455×105</t>
+          <t>795×695, s=5,9</t>
         </is>
       </c>
       <c r="G111" s="2" t="n">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
+          <t>Раскрой по DXF (PSH24-052.01-01__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Труба ⌀40×2,4, L=850</t>
+          <t>Деталь 850×40×40</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>40×40, L=850</t>
+          <t>850×40×40</t>
         </is>
       </c>
       <c r="G117" s="2" t="n">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Труба ⌀40×2,4, L=850</t>
+          <t>Деталь 850×40×40</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>40×40, L=850</t>
+          <t>850×40×40</t>
         </is>
       </c>
       <c r="G118" s="2" t="n">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Труба ⌀36×2,4, L=1050</t>
+          <t>Деталь 1050×36×36</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>36×36, L=1050</t>
+          <t>1050×36×36</t>
         </is>
       </c>
       <c r="G119" s="2" t="n">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Труба ⌀36×2,1, L=350</t>
+          <t>Деталь 350×36×36</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>36×36, L=350</t>
+          <t>350×36×36</t>
         </is>
       </c>
       <c r="G120" s="2" t="n">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 60×41,4×1,2, L=248,4</t>
+          <t>Панель гнутая, s=3,7</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -5399,12 +5399,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>60×41,4, L=248,4</t>
+          <t>258×64, s=3,7</t>
         </is>
       </c>
       <c r="G121" s="2" t="n">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Раскрой по DXF (PSH24-061.01__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Деталь 1184×500×50</t>
+          <t>Панель гнутая, s=4,9</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Заготовка (уточнить)</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>1184×500×50</t>
+          <t>1231×544, s=4,9</t>
         </is>
       </c>
       <c r="G123" s="2" t="n">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
+          <t>Раскрой по DXF (PSH24-070.01__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 35,4×19×1,4, L=1174</t>
+          <t>Деталь 1174×35,4×19</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Труба/профиль</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>35,4×19, L=1174</t>
+          <t>1174×35,4×19</t>
         </is>
       </c>
       <c r="G124" s="2" t="n">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер на ленточнопильном станке</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Стержень ⌀16, L=500</t>
+          <t>Деталь 500×16×16</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Пруток</t>
+          <t>Заготовка (уточнить)</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Ø16, L=500</t>
+          <t>500×16×16</t>
         </is>
       </c>
       <c r="G125" s="2" t="n">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>Распиловка в размер; дальнейшая обработка по чертежу</t>
+          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Деталь 86×80×60</t>
+          <t>Панель гнутая, s=2,7</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Заготовка (уточнить)</t>
+          <t>Лист гнутый (заготовка)</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>86×80×60</t>
+          <t>89×146, s=2,7</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Заготовка по технологу (сварная/литая), см. чертёж</t>
+          <t>Раскрой по DXF (PSH24-070.04__заготовка.dxf); гибка по чертежу, размеры заготовки уточнить по КД гибки</t>
         </is>
       </c>
     </row>
